--- a/lockring.xlsx
+++ b/lockring.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github-remote-fold-V1.1p\Github-remote-fold-V2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github-remote-fold-distribute-V1.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31F7D3D8-D9F2-4489-AFC2-A59D842A5F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE4515E-7D97-4AD5-BC2D-04D9974E2D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{02909DCD-F50C-4CF1-B9FE-33B3B5C85AC8}"/>
+    <workbookView xWindow="34785" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{02909DCD-F50C-4CF1-B9FE-33B3B5C85AC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>NO</t>
   </si>
@@ -44,193 +42,99 @@
     <t>Where to use (mm)</t>
   </si>
   <si>
-    <t>PART NUMBER</t>
-  </si>
-  <si>
     <t>CONNECTOR NAME</t>
   </si>
   <si>
-    <t>Pipe</t>
-  </si>
-  <si>
-    <t>SIZE(mm)</t>
-  </si>
-  <si>
-    <r>
-      <t>SIZE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(inch)</t>
-    </r>
-  </si>
-  <si>
     <t>Drier Inlet(1Eva, 2Eva) / Drier Outlet(2Eva)</t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63048101 </t>
-  </si>
-  <si>
     <t>LR 4 NK Ms 00</t>
   </si>
   <si>
-    <t>‘5/32</t>
-  </si>
-  <si>
     <t xml:space="preserve">Condenser connection(4.76) </t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63047101 </t>
-  </si>
-  <si>
     <t>LR 5 NK Ms 00</t>
   </si>
   <si>
-    <t>‘3/16</t>
-  </si>
-  <si>
     <t xml:space="preserve">Condenser(4.76) + Hot Line(4.0) </t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63047801 </t>
-  </si>
-  <si>
     <t>LR 5/4 NR Ms 00</t>
   </si>
   <si>
     <t>4.76 / 4</t>
   </si>
   <si>
-    <t>‘3/16 : 5/32</t>
-  </si>
-  <si>
     <t xml:space="preserve">Comp high side pipe </t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63047901 </t>
-  </si>
-  <si>
     <t>LR 7/5 NR Ms 00</t>
   </si>
   <si>
     <t>7 / 4.76</t>
   </si>
   <si>
-    <t xml:space="preserve">      - : ‘3/16</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.0 Pipe connection </t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63047501 </t>
-  </si>
-  <si>
     <t>LR 8 NK Ms 00</t>
   </si>
   <si>
-    <t>‘5/16</t>
-  </si>
-  <si>
     <t>Comp suction pipe, Process pipe</t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63048001 </t>
-  </si>
-  <si>
     <t>LR 8/6 NR Ms 00</t>
   </si>
   <si>
     <t>8 / 6.35</t>
   </si>
   <si>
-    <t>‘5/16 : 1/4</t>
-  </si>
-  <si>
     <t>L shape Lokring : Comp process pipe</t>
   </si>
   <si>
     <t>MGZ65560901</t>
   </si>
   <si>
-    <t>8 NWK Ms SVC 00</t>
-  </si>
-  <si>
     <t>6.35 / -</t>
   </si>
   <si>
-    <t>‘1/4</t>
-  </si>
-  <si>
     <t>T Charging(Comp+S/Pipe)</t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63447001 </t>
-  </si>
-  <si>
     <t>6 NK MS SV 00</t>
   </si>
   <si>
-    <t xml:space="preserve"> ‘1/4</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.35 Pipe connection </t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63047201 </t>
-  </si>
-  <si>
     <t>LR 6 NK Ms 00</t>
   </si>
   <si>
     <t>6.35 Evaporator – Capi (AL)</t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63447201 </t>
-  </si>
-  <si>
     <t>6/2 NR Al 00</t>
   </si>
   <si>
     <t>6.35 / 2</t>
   </si>
   <si>
-    <t>‘ 1/4 : 5/64</t>
-  </si>
-  <si>
     <t>8.0 Evaporator - Capi (AL)</t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63447202 </t>
-  </si>
-  <si>
     <t>8/2 NR Al 00</t>
   </si>
   <si>
-    <t>‘5/16  : 5/64</t>
-  </si>
-  <si>
     <t>6.35 Evaporator pipe connection (AL)</t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63047202 </t>
-  </si>
-  <si>
     <t>LR 6.35 NK Al 00</t>
   </si>
   <si>
     <t>8.0 Evaporator pipe connection (AL)</t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63047502 </t>
-  </si>
-  <si>
     <t>LR 8 NK Al 00</t>
   </si>
   <si>
@@ -246,21 +150,12 @@
     <t>8.5/8.5</t>
   </si>
   <si>
-    <t>- : -</t>
-  </si>
-  <si>
     <t>Drier – Capi tube</t>
   </si>
   <si>
-    <t xml:space="preserve">MGZ63048201 </t>
-  </si>
-  <si>
     <t>LR 4/2 NR Ms 00</t>
   </si>
   <si>
-    <t>‘5/32 : 5/64</t>
-  </si>
-  <si>
     <t>3.5 3way – 2.0 Capi</t>
   </si>
   <si>
@@ -297,9 +192,6 @@
     <t>4/3.2</t>
   </si>
   <si>
-    <t xml:space="preserve">‘5/32 : - </t>
-  </si>
-  <si>
     <t>4.0 Drier – 3.5 3way</t>
   </si>
   <si>
@@ -310,15 +202,122 @@
   </si>
   <si>
     <t>4/3.5</t>
+  </si>
+  <si>
+    <t>PARTNUMBER</t>
+  </si>
+  <si>
+    <t>사용부위</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PIPE Size</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MGZ63048101</t>
+  </si>
+  <si>
+    <t>4+4, Drier입출구</t>
+  </si>
+  <si>
+    <t>MGZ63047101</t>
+  </si>
+  <si>
+    <t>4.76+4.76 Cond</t>
+  </si>
+  <si>
+    <t>MGZ63047801</t>
+  </si>
+  <si>
+    <t>4.76+4.0 Cond+H/Line</t>
+  </si>
+  <si>
+    <t>MGZ63047901</t>
+  </si>
+  <si>
+    <t>7+4.76, Comp토출</t>
+  </si>
+  <si>
+    <t>MGZ63047501</t>
+  </si>
+  <si>
+    <t>8+8, Comp흡입(동-동연결)</t>
+  </si>
+  <si>
+    <t>MGZ63048001</t>
+  </si>
+  <si>
+    <t>8+6.35, Comp석션/Comp흡입</t>
+  </si>
+  <si>
+    <t>8 NWK MS SV 00</t>
+  </si>
+  <si>
+    <t>L자 락링용</t>
+  </si>
+  <si>
+    <t>MGZ63447001</t>
+  </si>
+  <si>
+    <t>T자 차징용</t>
+  </si>
+  <si>
+    <t>MGZ63047201</t>
+  </si>
+  <si>
+    <t>6.35+6.35 석션연결(동-동연결)</t>
+  </si>
+  <si>
+    <t>MGZ63447201</t>
+  </si>
+  <si>
+    <t>6.35+2.0 Eva+Capi</t>
+  </si>
+  <si>
+    <t>MGZ63447202</t>
+  </si>
+  <si>
+    <t>8.0+2.0 Eva+Capi</t>
+  </si>
+  <si>
+    <t>MGZ63047202</t>
+  </si>
+  <si>
+    <t>6.35+6.35 Eva(Al-Al연결)</t>
+  </si>
+  <si>
+    <t>MGZ63047502</t>
+  </si>
+  <si>
+    <t>8.0+8.0 Eva(Al-Al연결)</t>
+  </si>
+  <si>
+    <t>8.5+8.5 Eva</t>
+  </si>
+  <si>
+    <t>MGZ63048201</t>
+  </si>
+  <si>
+    <t>4+2, Drier+Capi</t>
+  </si>
+  <si>
+    <t>3.5+2.0 3way+Capi</t>
+  </si>
+  <si>
+    <t>3.5+3.5 3way</t>
+  </si>
+  <si>
+    <t>4.0+3.2 Drier+3way</t>
+  </si>
+  <si>
+    <t>4.0+3.5 Drier+3way</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -372,38 +371,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -427,9 +400,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -437,37 +419,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -804,484 +756,470 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F599BFA-99FB-458D-8470-E3F581F62E08}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="48" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="C2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="E2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7" t="s">
+    <row r="3" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="C3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="48" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
-        <v>1</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="E3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="9">
+    </row>
+    <row r="5" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="1">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
-        <v>2</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="C6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="E6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="10" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="9">
-        <v>4.76</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="C7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="36" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
-        <v>3</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="E7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="9" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="36" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
-        <v>4</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="D9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="48" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="1">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="1">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>11</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="B14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="1">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>12</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>13</v>
       </c>
-      <c r="E6" s="9">
-        <v>4.76</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
-        <v>5</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
-        <v>6</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="B17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="1">
         <v>8</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="9" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="C19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
-        <v>7</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="48" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="E19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="1">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="C20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="12">
-        <v>6.35</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="D20" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
-        <v>9</v>
-      </c>
-      <c r="B12" s="10" t="s">
+      <c r="E20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="9" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="C21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="9">
-        <v>6.35</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="36" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
-        <v>10</v>
-      </c>
-      <c r="B13" s="10" t="s">
+      <c r="D21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="E21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="10" t="s">
+    </row>
+    <row r="22" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="C22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="D22" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="36" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
-        <v>10</v>
-      </c>
-      <c r="B14" s="10" t="s">
+      <c r="E22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="9" t="s">
+    </row>
+    <row r="23" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="C23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="13">
-        <v>46236</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="D23" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
-        <v>11</v>
-      </c>
-      <c r="B15" s="10" t="s">
+      <c r="E23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="9">
-        <v>6.35</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
-        <v>12</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="9">
-        <v>8</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
-        <v>13</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
-        <v>14</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="9">
-        <v>8</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A19" s="9">
-        <v>14</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="13">
-        <v>46114</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="60" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
-        <v>15</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="9">
-        <v>6.35</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A21" s="9">
-        <v>17</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A22" s="9">
-        <v>18</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="36" x14ac:dyDescent="0.3">
-      <c r="A23" s="9">
-        <v>19</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A24" s="9">
-        <v>19</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>

--- a/lockring.xlsx
+++ b/lockring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github-remote-fold-distribute-V1.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE4515E-7D97-4AD5-BC2D-04D9974E2D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE3B93AD-4A0A-4FB5-98BA-A8D85F298758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34785" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{02909DCD-F50C-4CF1-B9FE-33B3B5C85AC8}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02909DCD-F50C-4CF1-B9FE-33B3B5C85AC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -758,6 +758,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F599BFA-99FB-458D-8470-E3F581F62E08}">
   <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
@@ -1222,6 +1229,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;12&amp;K000000 LGE Internal Use Only&amp;1#_x000D_</oddHeader>
   </headerFooter>
